--- a/source_of_truth_transcriptions.xlsx
+++ b/source_of_truth_transcriptions.xlsx
@@ -3144,7 +3144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>हेलो अनु दीदी मैं सीता बोल रही हूँ मेरा पेमेंट में हज़ार कम आया है आप ज़रा चेक करके देखिए ना। मैंने ना दो संडे को मैंने टेलीविज़न का काम किया था एक एक बार मैंने शूटिंग का काम किया था और एक बार टेलीविज़न का काम किया आप देख के बताइए</t>
+          <t>हेलो अनु दीदी मैं सीता बोल रही हूँ मेरा पेमेंट में हज़ार रुपया कम आया है आप ज़रा चेक करके देखिए ना। मैंने ना दो संडे को मैंने टेलीविज़न का काम किया था एक एक बार मैंने शूटिंग का काम किया था और एक बार टेलीविज़न का काम किया आप देख के बताइए</t>
         </is>
       </c>
     </row>
